--- a/ExcelRAddIn/Tests/Data Visualization.xlsx
+++ b/ExcelRAddIn/Tests/Data Visualization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\ExcelRAddIn\Tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AA6A23-B418-4B7B-A138-A7A945CAC43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEA4474-98EF-40A4-A75F-064ACA033046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{103A4457-AAC3-437C-9223-33DC1020895A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{103A4457-AAC3-437C-9223-33DC1020895A}"/>
   </bookViews>
   <sheets>
     <sheet name="References" sheetId="1" r:id="rId1"/>
@@ -333,9 +333,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -373,7 +373,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -479,7 +479,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -621,7 +621,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -673,7 +673,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="str" cm="1">
-        <f t="array" ref="D2">TRANSPOSE(_xll.RScript.Evaluate(B2, "true"))</f>
+        <f t="array" ref="D2">TRANSPOSE(_xll.RScript.Evaluate(B2, TRUE))</f>
         <v>OK</v>
       </c>
     </row>
@@ -682,7 +682,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="str" cm="1">
-        <f t="array" ref="D3">TRANSPOSE(_xll.RScript.Evaluate(B3,"true"))</f>
+        <f t="array" ref="D3">TRANSPOSE(_xll.RScript.Evaluate(B3,TRUE))</f>
         <v>OK</v>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C3A1991-1524-4EB5-BD98-B978A9A1B11E}">
-  <dimension ref="B2:K23"/>
+  <dimension ref="B2:C23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="64.109375" bestFit="1" customWidth="1"/>
@@ -2059,40 +2059,16 @@
         <v>plot_data</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C17" t="str" cm="1">
-        <f t="array" ref="C17:K17">TRANSPOSE(_xll.RScript.Evaluate(B17))</f>
-        <v>data</v>
-      </c>
-      <c r="D17" t="str">
-        <v>layers</v>
-      </c>
-      <c r="E17" t="str">
-        <v>scales</v>
-      </c>
-      <c r="F17" t="str">
-        <v>mapping</v>
-      </c>
-      <c r="G17" t="str">
-        <v>theme</v>
-      </c>
-      <c r="H17" t="str">
-        <v>coordinates</v>
-      </c>
-      <c r="I17" t="str">
-        <v>facet</v>
-      </c>
-      <c r="J17" t="str">
-        <v>plot_env</v>
-      </c>
-      <c r="K17" t="str">
-        <v>labels</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+        <f t="array" ref="C17">TRANSPOSE(_xll.RScript.Evaluate(B17, TRUE))</f>
+        <v>Exception: Unable to display the contents. Unknown expression type.</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>17</v>
       </c>
@@ -2101,7 +2077,7 @@
         <v>plot_data</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
@@ -2110,7 +2086,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>19</v>
       </c>
